--- a/output/pdf_financials_xlsx/EVER.xlsx
+++ b/output/pdf_financials_xlsx/EVER.xlsx
@@ -1406,19 +1406,19 @@
         <v>2.247406</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>2.973189</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.596109</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.237389</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.147874</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.00814</v>
       </c>
     </row>
     <row r="35">
@@ -1462,19 +1462,19 @@
         <v>2.247406</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>2.973189</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.596109</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.237389</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.147874</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.00814</v>
       </c>
     </row>
     <row r="37">
@@ -1798,19 +1798,19 @@
         <v>0.01966</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>3.021089</v>
+        <v>0.0479</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.630561</v>
+        <v>0.034452</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.259297</v>
+        <v>0.021908</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.158116</v>
+        <v>0.010242</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.00814</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -13303,7 +13303,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">

--- a/output/pdf_financials_xlsx/EVER.xlsx
+++ b/output/pdf_financials_xlsx/EVER.xlsx
@@ -884,10 +884,10 @@
         <v>0.03735</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.062296</v>
+        <v>-0.062296</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.046431</v>
+        <v>-0.046431</v>
       </c>
     </row>
     <row r="18">
@@ -3313,13 +3313,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.006682</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.080774</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.006116</v>
       </c>
       <c r="E101" s="3" t="n">
         <v>-0.024482</v>
@@ -3453,13 +3453,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.051952</v>
+        <v>0.04527</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.01529</v>
+        <v>-0.065484</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.038311</v>
+        <v>-0.044427</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>-0.055335</v>
@@ -7765,7 +7765,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E70" s="5" t="n">
         <v>-0.006682</v>
       </c>
@@ -9144,7 +9148,11 @@
           <t>Income tax recovery (note 14)</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
